--- a/BOOPTHAT Bill of Materials.xlsx
+++ b/BOOPTHAT Bill of Materials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fourc\Documents\Research\Equipment\High Throughput Laser Microheater\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Writings\Papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B246EBFA-4E7C-4A16-B7A4-DE3D2E020B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7262A92-E671-4AE6-9FEA-F2578DA25901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C04FBF1D-CB9A-4D11-B474-D68533E9FB83}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C04FBF1D-CB9A-4D11-B474-D68533E9FB83}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,23 +36,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t># Needed</t>
-  </si>
-  <si>
     <t>Link</t>
   </si>
   <si>
-    <t>Unit Cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Cost: </t>
-  </si>
-  <si>
     <t>https://www.culturehustleusa.com/collections/black/products/black-4-0</t>
   </si>
   <si>
@@ -65,9 +56,6 @@
     <t>https://www.amazon.com/Vallejo-Black-Primer-Acry-Poly-200ml/dp/B004BMZVMK/ref=sr_1_5?crid=3F1UBO7G7ZTKD&amp;dib=eyJ2IjoiMSJ9.t-SXwWdqmrszCygsAv1U4_UKq6_KzMMcIy--3nfn8h5S8gSrGBSmA2mqMguoLIx0IEnWwueiFpXNsSHEQKCRqKYYBp6letRIfxjoSp_u5xIVQqQiRoR86cGBh44TWoe-2O8UKypLAlMNpIFhRNBjqHcxMZL2et-gLDRU3PULJgyF0j8BTNHAkmDWTI75rLugTTYvPeEKD5bIo99xBZpA5QmnqMaMuyWu23Z91Boi9cfbdWm1sCLjiym7qT2eS6Q0nnI1ebYsO5tMFNePg5QRQQzf_oIVNG1qn6rO3Qat3oM.O3MaS5gA-RC6ZTGBKWqnApjZfH3kw4MFMJb_NJqz-84&amp;dib_tag=se&amp;keywords=black%2Bacrylic%2Bprimer&amp;qid=1708473887&amp;sprefix=black%2Bacrylic%2Bprimer%2Caps%2C69&amp;sr=8-5&amp;th=1</t>
   </si>
   <si>
-    <t>Visual Fault Locator 3 pack</t>
-  </si>
-  <si>
     <t>https://www.amazon.com/FYBOPTWU-Visual-Locator-Singlemode-Adapter/dp/B0BXP6ZKTF/ref=sr_1_11?crid=3R58H7QCQ7TY3&amp;dib=eyJ2IjoiMSJ9.KwWXlJUHh44uj7ULeefyI6TRdf0ezF9ZQlOqGHlxy4zuhJ96Ph4kwJG5lJknBiVUTCR0ksoi1QDY4-qL6SYWJ93xeaZbRgof8fnwPJcWUsMWKc710MgHpl3D5sfQjzs1t5FHfwZCZeCNkULpGo6aEpQY4ifqk8NwSVSNjHkxYgSta6UF2vY3WUlhJhx_5myQ4MAF_W-KAy9idOtyJiM1eaVYFBM-nvOQS_VpMIirAOQ.RBvvWKwaWPmmHn5YS96vZNr0EakWGkEjDvgRBTu6yec&amp;dib_tag=se&amp;keywords=visual%2Bfault%2Blocator%2B30mW&amp;qid=1708473963&amp;sprefix=visual%2Bfault%2Blocator%2B30mw%2Caps%2C77&amp;sr=8-11&amp;th=1</t>
   </si>
   <si>
@@ -80,12 +68,6 @@
     <t>https://accu-components.com/</t>
   </si>
   <si>
-    <t>Laser Power Meter</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Sper-Scientific-840011-Laser-Power/dp/B001EUEU1U</t>
-  </si>
-  <si>
     <t>Grip Tape</t>
   </si>
   <si>
@@ -101,21 +83,9 @@
     <t>Hardware - 50 M4x40, 75 M4 Hex, 25 M3x10, 25 M3 Hex</t>
   </si>
   <si>
-    <t>Visual Fault Locator</t>
-  </si>
-  <si>
-    <t>10 ohm trimmer potentiometer (10 pack)</t>
-  </si>
-  <si>
     <t>20 AWG wire</t>
   </si>
   <si>
-    <t>T-tap wire connector (24 pack)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/HPOYUELC-Transmitter-Suitable-Universal-Connector/dp/B09XL2ND4J/ref=sr_1_1_pp?crid=K8PGUG7U2MSL&amp;dib=eyJ2IjoiMSJ9.eZ__FIgxhZp-vKy8nB4EbnV3ah1joG9OblaxqgdoOLVKZHTTsNFxnj27tZJ65n3-ea_qK7l0xs406zg1rJH_jYaxZ6F6RtXb_vq8krYBJd7lnnkyL-_BT9N8edwLfQegqWLfgT6ZwDAczVvVbo6ehnKYRnCLpYwmRaorUDyM_b3W2oUaDTFCz2xf9oOLO7bZbNf21Dx-vTXoJ4GDB1BiM2r9yEAUc9cbV0Gis6zLRr5QDKLoGcm5iZjZ5fwVZdPEPVzs7z7Jaquz16v0Fa0oKMeEwbnenIhSM8dwmvUjWTI.6NTtTMKoc4B-v8O9CkotvEzn58C8FUL6ZQtLZd0R13s&amp;dib_tag=se&amp;keywords=vfl&amp;qid=1710157952&amp;s=industrial&amp;sprefix=vfl%2Cindustrial%2C78&amp;sr=1-1</t>
-  </si>
-  <si>
     <t>https://www.amazon.com/Silicone-Electrical-Conductor-Parallel-Flexible/dp/B07K9JKXM9/ref=sr_1_4?crid=3V339BFFDZ8VS&amp;dib=eyJ2IjoiMSJ9.WNUWgIHBQWtcWKfS11vHyb2_2MVRAuAIdm6gfTLhmzCaUfRdw_Yea_GZq92ViHJa0dU71qMadsS3KZD16VD0mwJIe0QkgPo1TS1XDcmiQYFMciLvy3ptq1KchpJDR2VvnC0a3GPsDuuIY8qsecMN_gH-cSbCCT1-AODdsGLSJGSfTrFOIRrRzOQjMTN4IN-07WsV9-CFB5uT9AnFeT88S_Fy_N3PnmYh0kols9n6kGCcwUZzzV_95PSX8BxW6bM4vYvx0gbVQyYkvFwMBrEl8k8jR8mbigondL91v2MMEDk.FocKi0YbsZFWx4dVdBDjlDY89sv0b6bhhTWmk2WQiAE&amp;dib_tag=se&amp;keywords=20%2Bawg%2Bwire&amp;qid=1710157594&amp;s=hi&amp;sprefix=20%2Bawg%2Bwire%2Ctools%2C105&amp;sr=1-4&amp;th=1</t>
   </si>
   <si>
@@ -128,33 +98,15 @@
     <t>https://www.amazon.com/Brightfour-Voltage-Connectors-Stripping-24-18/dp/B0BLKBQ2JH/ref=sr_1_8?crid=1O0UBGR3GMJAY&amp;dib=eyJ2IjoiMSJ9.VwF37Y7cDpdsk-XbzNewsoBO3TUxC7rX0e4ekP3bX2z20q7UUl8OV4Hf_jhGeXJymo0QpGpuiF_abYvbPVufQBQyzzuKPtnZlMMuLyyPKNp3f3F62JZO--BxXoqN8FdJvC-JnJtRX2z7aMiQYnkfz91dhXchLZFibkQEXLViomaE4cX-PVk_jpLs0mTZPBEqLjftE5UHE2geZ5d2gYy7bgMJtA8TYlSAQx5Xo8y9_lqsrwEM8d2FjcPlgHoTTm0ZvE1Y8rBrfWKIk9gawEbKHn12AP79WYqbs1y8BoLpo0A.1OPjtHfMtmfxZuzZtVKPxQHrVKehgJ8RVydwRRc5K1M&amp;dib_tag=se&amp;keywords=2%2Bwire%2Bt%2Bconnector&amp;qid=1710119331&amp;s=hi&amp;sprefix=2%2Bwire%2Bt%2Bconnector%2Ctools%2C106&amp;sr=1-8&amp;th=1</t>
   </si>
   <si>
-    <t>Black CA Glue</t>
-  </si>
-  <si>
-    <t>Black Epoxy</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Premium-Grade-Cyanoacrylate-Super-STARBOND/dp/B00C32MMFO/ref=sr_1_3?dib=eyJ2IjoiMSJ9.iD6c5WFVwNhT9sQ0nHqCAWFL900EchJJULpwmgkNsvTng5EneetrK01IxOjbtqmkDAVRx6GXy7bQK3yYmEZCGLMEdP0dv589X_PSy0pE8V0tjFTcCO-ZiTPVLZK5NsGlN5jx-IlbjkoUE6-IKKMmm6uPEMaWrhkK2EaobVhlUDUhJxyk8ndJVL3c8N1MvziDpZ8DIRlSaSdwzMvNijO9oLZdyGmOTLaPKSBLVKbyxck.z4TFlgrdXLmm5URn77NXl-peR9Hj_UVOkXyBPXfTUkA&amp;dib_tag=se&amp;keywords=black%2Bsuperglue&amp;qid=1710157323&amp;sr=8-3&amp;th=1</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Gorilla-Ultimate-Waterproof-Permanent-Syringe/dp/B0CLPLQS24/ref=sr_1_1?crid=1S5J8K0S17FNH&amp;dib=eyJ2IjoiMSJ9.o53rZQHBYsNjJvbjU1DMPNx58eiCP2rh0S1W50l7myB4O8D-gK12xqy7hTAedAjqhE1-irSlxtaY3JKrqxflCTsHKqwWA4gjTi4o8jvRiLqDKS3QGRgq3i2F6N9LvJ5X69l6Pr-vuO_XWIDcHkLRztnVdJ_OEGGOVgYUdZMAfDF6ilxlVYk4527eEfX2Eh50VFgtXoL9bBpHgOY05qCVLuINoe4HoRwmcsftErFZvzU.j5jwgcud7hsam5UIyKtG4afEcPs-eeirHuNcdRGNY3I&amp;dib_tag=se&amp;keywords=black%2Bepoxy&amp;qid=1710121440&amp;sprefix=black%2Bepoxy%2Caps%2C86&amp;sr=8-1&amp;th=1</t>
-  </si>
-  <si>
     <t>Thermocouple Reader</t>
   </si>
   <si>
     <t>E-type thermocouple connector</t>
   </si>
   <si>
-    <t>https://www.amazon.com/Proster-Thermocouple-Thermometer-Dual-Channel-Thermocouples/dp/B071V7T6TZ/ref=sr_1_3?crid=3IQZNTREKDOYJ&amp;dib=eyJ2IjoiMSJ9.QBKO8-Hu1hSlo5J7nz3NRMPchTuXIRY2wodi2d7Df-dzAphQQoVI-Lwbua26ndLynHdU7IRi4KnWcSmB22U46QICnMPlkHgnb6jdpTDKeE5R_1pkIswVda2T5GJ_7hsv5S2JKt8Wlbbtl2sJnX6W1wEq3wYkzmAPnz0bhQQVzUmpq3dBDSJRaeSWp5Ql6fDKfC-fV9EwGT-JWkJJkAlL8phcB6EtPieq0ftvMNejAHs.db2MYQNI4G77fvUl5aSkCK5_O0dUaTV5ydLWxZwN8wQ&amp;dib_tag=se&amp;keywords=e-type+thermocouple+reader&amp;qid=1710962874&amp;sprefix=e-type+thermocouple+reader%2Caps%2C116&amp;sr=8-3</t>
-  </si>
-  <si>
     <t>https://www.amazon.com/MECCANIXITY-Thermocouple-Connectors-Adapter-Temperature/dp/B0C348T7KD/ref=sr_1_1?crid=1FCGPP2SW2SGS&amp;dib=eyJ2IjoiMSJ9.FC1hpYHfXh-inzX4Ui4fFFc9Sv2kp-f_mVspJq3Jt-m3czUEReZFLXJEo2oZ90dzhya5FyEPIexGQTe3RkhPCsIruHPmo2O81bmcX5i6xbGQ5mIATUAt9NetvOXyXgHumOjUmlgmxiVDaoWRm8IWrfhCGEQVY32gg5h0YQmuCvClflfLagXUBIAh58s0w_axpbIbAFqa9QahoFxGEl1y-T_VzSB6rB5wxuBsMBNigSU.dJWB5QVTY-hJwQQDH-DMXN41C8iUgZgvfNgbSZ6WJ7U&amp;dib_tag=se&amp;keywords=e-type+thermocouple+connector&amp;qid=1710962960&amp;sprefix=e-type+thermocouple+connector%2Caps%2C70&amp;sr=8-1</t>
   </si>
   <si>
-    <t>BOOPTHAT BOM V4</t>
-  </si>
-  <si>
     <t>56 AWG thermocouple wire E,T(-)</t>
   </si>
   <si>
@@ -164,28 +116,50 @@
     <t>https://www.omega.com/en-us/temperature-measurement/temperature-wire-and-cable/extension-wires-and-cables/spir/p/SPCH-0005-50</t>
   </si>
   <si>
-    <t>Already Ordered</t>
-  </si>
-  <si>
-    <t>To Order</t>
+    <t>BOOPTHAT Bill of Materials</t>
+  </si>
+  <si>
+    <t>For building the setup</t>
+  </si>
+  <si>
+    <t>For calibrating the setup</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/FiberCablesDirect-ST-ST-Fiber-Patch-Cable/dp/B01663TVFY/ref=sr_1_2_sspa?crid=2PZDPWMFB5CMQ&amp;dib=eyJ2IjoiMSJ9.bssbXSp2xmXw4xMbbOwralWslxBZOdEPLHLId_nvH4HCAeyuXFnhOqetqs401qiVHU6dlOGBEKhsS-6RLCesHL1G4aMCz2Tx_sVPMY85eRPk1WgtH1pDm0hDn0thdcX8iRRbTRfMeHvy7Tbxu8iQph40iibmLaTcODmSxIESNL-9-IGeYdLgLJhwdnR3v8hqhv2i5kuxShmu7RklkgM0I0af5jaWtHCsJGhRA5azUQqs0fTX9uBsjIOySygBFGLrpVV_7kYMLIPmpqe3rr2nLhba-N-qutAEZbfzzFMvxSA.sHrQrli-vJtOVbpiXrTaZmp0V3MOqXdZgQanFX9L4jw&amp;dib_tag=se&amp;keywords=ST%2Bconnector%2Boptical%2Bfiber&amp;qid=1780408552&amp;s=industrial&amp;sprefix=st%2Bconnector%2Boptical%2Bfiber%2Cindustrial%2C400&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>Optical Fiber, ST connectors, multimode with wide core</t>
+  </si>
+  <si>
+    <t>Laser Power Meter, Sanwa LP10</t>
+  </si>
+  <si>
+    <t>https://www.sanwa-america.com/products/lp10-laser-power-meter?srsltid=AfmBOornC2bTYIF3ILdSAg1wTCDolluzlg8iZBbC6PXIGqC1ACjfOU7m</t>
+  </si>
+  <si>
+    <t>30 mW visual fault locators</t>
+  </si>
+  <si>
+    <t>T-tap wire connector</t>
+  </si>
+  <si>
+    <t>10 ohm trimmer potentiometer</t>
+  </si>
+  <si>
+    <t>Probe cutting/coating</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Fluke-Calibrated-Single-Input-Thermometer/dp/B000VRCSX4/ref=sr_1_1_sspa?crid=G855DIJ65KZ6&amp;dib=eyJ2IjoiMSJ9.9Cn_wewxEoC19Qrg2SCj1QgHwQYdZwAeDWMPMN-VO0nxMO258ecMQLiPjUnlzr5dd5SWOkgXU8fdNNjeL8UycU_mYi8wRYwaRhgkjFRb9b55kQBtBvRyBwqfmWZoVSlCf-o3VXsNcUNdHALnAZWDTWTEG_H7fOMd-XfpvncQMY-Sex_qb22cXNAnsUBYUTJ9eNlYa9abkGuMkwWucBNrsaWH90ufKm75JQPt8dcUyEQ.PxQFbFrKupPZ1oYZQsVdu0texKEv59Sji_4dx2ZAIUA&amp;dib_tag=se&amp;keywords=fluke+thermocouple+reader&amp;qid=1780409596&amp;sprefix=fluke+thermocouple+read%2Caps%2C300&amp;sr=8-1-spons&amp;ufe=app_do%3Aamzn1.fos.5998aa40-ec6f-4947-a68f-cd087fee0848&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>Notes: The specific brands and quantities can be changed based on need and availability. The links provided are the ones that we used, with the exception of the optical fiber. We used optical fiber that we had on hand. The important specs for the optical fiber - it should be multimode (wider core, &gt;50um), have ST connectors on both ends so that both halves can be used.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-  </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,12 +194,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -239,7 +207,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -252,8 +220,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -262,19 +242,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -351,66 +318,139 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -723,362 +763,317 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90221D44-CDFC-469F-87EA-9F3AB247B1CA}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.21875" style="19" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="19"/>
-    <col min="3" max="3" width="16.6640625" style="19" customWidth="1"/>
-    <col min="4" max="6" width="8.88671875" style="19"/>
-    <col min="7" max="7" width="28.88671875" style="19" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" style="19" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" style="19" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="47.5546875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="25" style="6" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" style="6"/>
+    <col min="5" max="5" width="28.88671875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="17.109375" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="14"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="27" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="G3" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="26"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="29"/>
+    </row>
+    <row r="5" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="32"/>
+    </row>
+    <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="32"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="32"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="32"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="32"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="32"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="32"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="32"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="19"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="32"/>
+    </row>
+    <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="32"/>
+    </row>
+    <row r="15" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="26"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="32"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="6">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="7">
-        <v>52.99</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="19">
-        <v>1</v>
-      </c>
-      <c r="I5" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="20">
-        <v>18.350000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="7">
-        <v>16.14</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="19">
-        <v>1</v>
-      </c>
-      <c r="I6" s="23" t="s">
+      <c r="C16" s="25"/>
+      <c r="D16" s="26"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="32"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="7"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="32"/>
+    </row>
+    <row r="18" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="32"/>
+    </row>
+    <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="32"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="32"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="20">
-        <v>9.2899999999999991</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="6">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="7">
-        <v>14.51</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="19">
-        <v>1</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" s="20">
-        <v>109.43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="7">
-        <v>241</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="J8" s="20"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7">
-        <v>9.99</v>
-      </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="18">
-        <f>SUMPRODUCT(H5:H8,J5:J8)</f>
-        <v>137.07</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="7">
-        <v>49.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="6">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="7">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="13">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="32"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="6">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="7">
-        <v>16.489999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="B22" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="9">
-        <v>2</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="7">
-        <v>12.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="6">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="7">
-        <v>18.98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6">
-        <v>1</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="7">
-        <v>22.99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="6">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="7">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="6">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="7">
-        <v>19.489999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="12">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="13">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="6">
-        <v>1</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="7">
-        <v>109.43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="14"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="18">
-        <f>SUMPRODUCT(B5:B20,D5:D20)</f>
-        <v>802.90000000000009</v>
-      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="35"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="8"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:J3"/>
+  <mergeCells count="6">
+    <mergeCell ref="F4:I22"/>
+    <mergeCell ref="C14:D16"/>
+    <mergeCell ref="C18:D22"/>
+    <mergeCell ref="C5:D12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" display="https://www.amazon.com/FYBOPTWU-Visual-Locator-Singlemode-Adapter/dp/B0BXP6ZKTF/ref=sr_1_11?crid=3R58H7QCQ7TY3&amp;dib=eyJ2IjoiMSJ9.KwWXlJUHh44uj7ULeefyI6TRdf0ezF9ZQlOqGHlxy4zuhJ96Ph4kwJG5lJknBiVUTCR0ksoi1QDY4-qL6SYWJ93xeaZbRgof8fnwPJcWUsMWKc710MgHpl3D5sfQjzs1t5FHfwZCZeCNkULpGo6aEpQY4ifqk8NwSVSNjHkxYgSta6UF2vY3WUlhJhx_5myQ4MAF_W-KAy9idOtyJiM1eaVYFBM-nvOQS_VpMIirAOQ.RBvvWKwaWPmmHn5YS96vZNr0EakWGkEjDvgRBTu6yec&amp;dib_tag=se&amp;keywords=visual%2Bfault%2Blocator%2B30mW&amp;qid=1708473963&amp;sprefix=visual%2Bfault%2Blocator%2B30mw%2Caps%2C77&amp;sr=8-11&amp;th=1" xr:uid="{4296C450-05BA-4398-B8DF-9F0B0A93C537}"/>
-    <hyperlink ref="C11" r:id="rId2" xr:uid="{17314B90-D054-4702-A9BA-021313F7E2C8}"/>
-    <hyperlink ref="C8" r:id="rId3" xr:uid="{E533522A-DCE5-4F7F-93E4-5BF329A5F699}"/>
-    <hyperlink ref="I5" r:id="rId4" display="https://www.amazon.com/Proster-Thermocouple-Thermometer-Dual-Channel-Thermocouples/dp/B071V7T6TZ/ref=sr_1_3?crid=3IQZNTREKDOYJ&amp;dib=eyJ2IjoiMSJ9.QBKO8-Hu1hSlo5J7nz3NRMPchTuXIRY2wodi2d7Df-dzAphQQoVI-Lwbua26ndLynHdU7IRi4KnWcSmB22U46QICnMPlkHgnb6jdpTDKeE5R_1pkIswVda2T5GJ_7hsv5S2JKt8Wlbbtl2sJnX6W1wEq3wYkzmAPnz0bhQQVzUmpq3dBDSJRaeSWp5Ql6fDKfC-fV9EwGT-JWkJJkAlL8phcB6EtPieq0ftvMNejAHs.db2MYQNI4G77fvUl5aSkCK5_O0dUaTV5ydLWxZwN8wQ&amp;dib_tag=se&amp;keywords=e-type+thermocouple+reader&amp;qid=1710962874&amp;sprefix=e-type+thermocouple+reader%2Caps%2C116&amp;sr=8-3" xr:uid="{7EDDB5AD-F5F9-4AC2-B732-CE68C3B3A523}"/>
-    <hyperlink ref="I6" r:id="rId5" display="https://www.amazon.com/MECCANIXITY-Thermocouple-Connectors-Adapter-Temperature/dp/B0C348T7KD/ref=sr_1_1?crid=1FCGPP2SW2SGS&amp;dib=eyJ2IjoiMSJ9.FC1hpYHfXh-inzX4Ui4fFFc9Sv2kp-f_mVspJq3Jt-m3czUEReZFLXJEo2oZ90dzhya5FyEPIexGQTe3RkhPCsIruHPmo2O81bmcX5i6xbGQ5mIATUAt9NetvOXyXgHumOjUmlgmxiVDaoWRm8IWrfhCGEQVY32gg5h0YQmuCvClflfLagXUBIAh58s0w_axpbIbAFqa9QahoFxGEl1y-T_VzSB6rB5wxuBsMBNigSU.dJWB5QVTY-hJwQQDH-DMXN41C8iUgZgvfNgbSZ6WJ7U&amp;dib_tag=se&amp;keywords=e-type+thermocouple+connector&amp;qid=1710962960&amp;sprefix=e-type+thermocouple+connector%2Caps%2C70&amp;sr=8-1" xr:uid="{EA219B21-E59E-43BB-A7A9-6BB8BBC60569}"/>
-    <hyperlink ref="I7" r:id="rId6" xr:uid="{E419108D-52AB-46A4-BF25-3DD87F39AF4C}"/>
+    <hyperlink ref="B6" r:id="rId1" display="https://www.amazon.com/OVERTURE-Filament-Consumables-Dimensional-Accuracy/dp/B07PGYHYV8/ref=sr_1_4?crid=3DNTX784ABTRD&amp;dib=eyJ2IjoiMSJ9.yf4QrGfdb01bS0owhB7XaEc31hd07POrmrkNF-mVmaCe15UCIiXF1juweOZrfCKMwjIk0OJpT2RmkFw8HVtfQ7GJDvwqGIJ_XjYahUChx-yy66-ezbjl4NAFEXna7GXNa89grsfEhYXokT-Qy2o9UzYGsCt6jxNMc-hdnIT-JTJWku8WVohhd6FMY2FWKfGzXLK7vGySlLdiIUXgzUFGLPIPMDw71OBkKrrgXK8x5IM.8A1pUqKSc7sOkHaMmBm0C-Jo24Pv5Q8Fxk3QurGRak8&amp;dib_tag=se&amp;keywords=petg&amp;qid=1708474435&amp;sprefix=petg%2Caps%2C87&amp;sr=8-4&amp;th=1" xr:uid="{5E0ED0E9-6988-4A85-B633-A78D65A8A8D6}"/>
+    <hyperlink ref="B5" r:id="rId2" display="https://www.amazon.com/FYBOPTWU-Visual-Locator-Singlemode-Adapter/dp/B0BXP6ZKTF/ref=sr_1_11?crid=3R58H7QCQ7TY3&amp;dib=eyJ2IjoiMSJ9.KwWXlJUHh44uj7ULeefyI6TRdf0ezF9ZQlOqGHlxy4zuhJ96Ph4kwJG5lJknBiVUTCR0ksoi1QDY4-qL6SYWJ93xeaZbRgof8fnwPJcWUsMWKc710MgHpl3D5sfQjzs1t5FHfwZCZeCNkULpGo6aEpQY4ifqk8NwSVSNjHkxYgSta6UF2vY3WUlhJhx_5myQ4MAF_W-KAy9idOtyJiM1eaVYFBM-nvOQS_VpMIirAOQ.RBvvWKwaWPmmHn5YS96vZNr0EakWGkEjDvgRBTu6yec&amp;dib_tag=se&amp;keywords=visual%2Bfault%2Blocator%2B30mW&amp;qid=1708473963&amp;sprefix=visual%2Bfault%2Blocator%2B30mw%2Caps%2C77&amp;sr=8-11&amp;th=1" xr:uid="{5213C1D1-7AC2-4319-8DF2-AF93F84FBE5C}"/>
+    <hyperlink ref="B7" r:id="rId3" xr:uid="{4CD3F9E0-FE35-4EB0-A7AC-5932428C8485}"/>
+    <hyperlink ref="B20" r:id="rId4" xr:uid="{C6CE5153-2205-4ADF-8F53-B5FB1CD3FE44}"/>
+    <hyperlink ref="B21" r:id="rId5" display="https://www.amazon.com/Proster-Thermocouple-Thermometer-Dual-Channel-Thermocouples/dp/B071V7T6TZ/ref=sr_1_3?crid=3IQZNTREKDOYJ&amp;dib=eyJ2IjoiMSJ9.QBKO8-Hu1hSlo5J7nz3NRMPchTuXIRY2wodi2d7Df-dzAphQQoVI-Lwbua26ndLynHdU7IRi4KnWcSmB22U46QICnMPlkHgnb6jdpTDKeE5R_1pkIswVda2T5GJ_7hsv5S2JKt8Wlbbtl2sJnX6W1wEq3wYkzmAPnz0bhQQVzUmpq3dBDSJRaeSWp5Ql6fDKfC-fV9EwGT-JWkJJkAlL8phcB6EtPieq0ftvMNejAHs.db2MYQNI4G77fvUl5aSkCK5_O0dUaTV5ydLWxZwN8wQ&amp;dib_tag=se&amp;keywords=e-type+thermocouple+reader&amp;qid=1710962874&amp;sprefix=e-type+thermocouple+reader%2Caps%2C116&amp;sr=8-3" xr:uid="{4083F5CA-B230-491B-9E7B-1D84F5615C96}"/>
+    <hyperlink ref="B22" r:id="rId6" display="https://www.amazon.com/MECCANIXITY-Thermocouple-Connectors-Adapter-Temperature/dp/B0C348T7KD/ref=sr_1_1?crid=1FCGPP2SW2SGS&amp;dib=eyJ2IjoiMSJ9.FC1hpYHfXh-inzX4Ui4fFFc9Sv2kp-f_mVspJq3Jt-m3czUEReZFLXJEo2oZ90dzhya5FyEPIexGQTe3RkhPCsIruHPmo2O81bmcX5i6xbGQ5mIATUAt9NetvOXyXgHumOjUmlgmxiVDaoWRm8IWrfhCGEQVY32gg5h0YQmuCvClflfLagXUBIAh58s0w_axpbIbAFqa9QahoFxGEl1y-T_VzSB6rB5wxuBsMBNigSU.dJWB5QVTY-hJwQQDH-DMXN41C8iUgZgvfNgbSZ6WJ7U&amp;dib_tag=se&amp;keywords=e-type+thermocouple+connector&amp;qid=1710962960&amp;sprefix=e-type+thermocouple+connector%2Caps%2C70&amp;sr=8-1" xr:uid="{B9D8BBDF-43D4-4079-BB8C-DEEC415EED81}"/>
+    <hyperlink ref="B19" r:id="rId7" xr:uid="{F112B878-5239-4359-B6C6-D88410B875FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
